--- a/site/leagues/proliga/2026_2027/xlsx/context_packs/context_pack_SLB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/context_packs/context_pack_SLB.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>64.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.3</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-5.3</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-2.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (1.5)</t>
+          <t>Q3 (1)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-8)</t>
+          <t>Q4 (-6.3)</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,19 +706,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: -6 | fora: -12</t>
+          <t>Diff médio casa: -2 | fora: -12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (1.5)</t>
+          <t>Diff médio em vitórias: 2 | em derrotas: -9</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-8)</t>
+          <t>Melhor período: Q3 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-6.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T. Filipe sobe mais em vitórias (6 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -746,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -873,8 +897,41 @@
         <v>-6</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>69</v>
+      </c>
+      <c r="H4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -973,150 +1030,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.9</v>
+        <v>28.3</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>-6</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
-        <v>29.5</v>
+        <v>36.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>-17</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-11.5</v>
+        <v>-3</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. Te</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.6</v>
+        <v>29.4</v>
       </c>
       <c r="C3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>-17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>-11.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. Viegas</t>
+          <t>W. Oliveira</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2</v>
+        <v>20.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. Oliveira</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.4</v>
+        <v>25.2</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>-3</v>
+        <v>-11.5</v>
       </c>
       <c r="E5" t="n">
-        <v>17.7</v>
+        <v>33.4</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
         <v>-11</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="L5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1125,13 +1206,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.3</v>
+        <v>35.7</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>-6</v>
+        <v>-0.5</v>
       </c>
       <c r="E6" t="n">
         <v>34.8</v>
@@ -1142,8 +1223,12 @@
       <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
       <c r="J6" t="n">
         <v>15.5</v>
       </c>
@@ -1151,120 +1236,140 @@
         <v>-1.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>G. Viegas</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.8</v>
+        <v>7.2</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>36.2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>-8</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>G. Te</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>10.1</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="E8" t="n">
-        <v>27.8</v>
+        <v>5.3</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-9</v>
+      </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.5</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.4</v>
+        <v>29.7</v>
       </c>
       <c r="C9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
         <v>13</v>
       </c>
-      <c r="G9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
       <c r="K9" t="n">
-        <v>-11</v>
+        <v>-3.5</v>
       </c>
       <c r="L9" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>-6</v>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1373,22 +1478,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1416,25 +1521,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
         <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1459,25 +1564,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H4" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1607,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="I5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-8</v>
+        <v>-6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1539,22 +1644,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1651,52 +1756,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -1706,147 +1811,147 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="D4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1855,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1871,40 +1976,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1916,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1929,25 +2034,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1956,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1980,7 +2085,9 @@
           <t>G. Te</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
         <v>0.5</v>
       </c>
@@ -1988,15 +2095,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
@@ -2004,7 +2115,9 @@
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
@@ -2023,33 +2136,41 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.5</v>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2064,11 +2185,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2171,8 +2292,37 @@
         <v>-12</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2923000</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>